--- a/R/inst/extdata/linear_threshold_results.xlsx
+++ b/R/inst/extdata/linear_threshold_results.xlsx
@@ -24,7 +24,7 @@
     <t xml:space="preserve">Cutoff</t>
   </si>
   <si>
-    <t xml:space="preserve">SBP</t>
+    <t xml:space="preserve">SOFA_CRRT_0h</t>
   </si>
   <si>
     <t xml:space="preserve">Beta</t>
@@ -414,7 +414,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -456,22 +456,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>5.384074898497</v>
+        <v>78.1626130325165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.376964896719892</v>
+        <v>24.8606558671432</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2826956709916</v>
+        <v>3.14402859885202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000000000000000000000000904252694385686</v>
+        <v>0.0017234542193784</v>
       </c>
       <c r="F2" t="n">
-        <v>4.64523727749015</v>
+        <v>29.4366229008716</v>
       </c>
       <c r="G2" t="n">
-        <v>6.12291251950384</v>
+        <v>126.888603164162</v>
       </c>
     </row>
     <row r="3">
@@ -479,22 +479,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.00650818147640904</v>
+        <v>0.994123355853054</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00237756113987804</v>
+        <v>1.07881009728209</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.73733506459602</v>
+        <v>0.92149986207731</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00642579490956447</v>
+        <v>0.357047341812475</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.011168115681612</v>
+        <v>-1.12030558097799</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00184824727120607</v>
+        <v>3.10855229268413</v>
       </c>
     </row>
     <row r="4">
@@ -502,22 +502,22 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0049672117822722</v>
+        <v>0.285450910066412</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00348419243350896</v>
+        <v>0.253427920279558</v>
       </c>
       <c r="D4" t="n">
-        <v>1.42564220463268</v>
+        <v>1.12635935989819</v>
       </c>
       <c r="E4" t="n">
-        <v>0.154627073635566</v>
+        <v>0.260326913237779</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00186167990261229</v>
+        <v>-0.211258686358408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0117961034671568</v>
+        <v>0.782160506491242</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +525,22 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0977837583299136</v>
+        <v>1.66962051212011</v>
       </c>
       <c r="C5" t="n">
-        <v>0.103850190372961</v>
+        <v>7.54477229271259</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.941584776866941</v>
+        <v>0.221295016912939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.346882873689091</v>
+        <v>0.824915139082853</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.301326391248544</v>
+        <v>-13.1178614531528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.105758874588716</v>
+        <v>16.4571024773924</v>
       </c>
     </row>
   </sheetData>
@@ -582,22 +582,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>4.68320782720471</v>
+        <v>94.8359707600229</v>
       </c>
       <c r="C2" t="n">
-        <v>0.272866196032644</v>
+        <v>19.97053617517</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1630194406508</v>
+        <v>4.74879442034888</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000010030965787635</v>
+        <v>0.00000239622558794203</v>
       </c>
       <c r="F2" t="n">
-        <v>4.14839991038228</v>
+        <v>55.6944391047356</v>
       </c>
       <c r="G2" t="n">
-        <v>5.21801574402713</v>
+        <v>133.977502415311</v>
       </c>
     </row>
     <row r="3">
@@ -605,22 +605,22 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0618938011462033</v>
+        <v>-2.47715739792757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0157471866475197</v>
+        <v>1.97203949808905</v>
       </c>
       <c r="D3" t="n">
-        <v>3.93046723402825</v>
+        <v>-1.25613984929206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000973859405953199</v>
+        <v>0.209406000295833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0310298824592341</v>
+        <v>-6.34228379027261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0927577198331703</v>
+        <v>1.3879689944174</v>
       </c>
     </row>
     <row r="4">
@@ -628,22 +628,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00244326165242109</v>
+        <v>-0.666033734355878</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00261222662252624</v>
+        <v>2.13978517712968</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.935317644859712</v>
+        <v>-0.311261962871104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.35009987487398</v>
+        <v>0.755676826750556</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00756313175202921</v>
+        <v>-4.85993561618279</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00267660844718704</v>
+        <v>3.52786814747103</v>
       </c>
     </row>
     <row r="5">
@@ -651,22 +651,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00493245143877703</v>
+        <v>0.275874419024579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00344232866767346</v>
+        <v>0.253680313646387</v>
       </c>
       <c r="D5" t="n">
-        <v>1.43288218963434</v>
+        <v>1.08748848130616</v>
       </c>
       <c r="E5" t="n">
-        <v>0.152549315866279</v>
+        <v>0.277125316237696</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00181438877281268</v>
+        <v>-0.221329859309164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0116792916503667</v>
+        <v>0.773078697358331</v>
       </c>
     </row>
     <row r="6">
@@ -674,22 +674,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.105250178523385</v>
+        <v>1.78433742945242</v>
       </c>
       <c r="C6" t="n">
-        <v>0.102623451337283</v>
+        <v>7.54669664813016</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.02559577905316</v>
+        <v>0.236439532771537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.305604156718644</v>
+        <v>0.813147859152927</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.306388447113657</v>
+        <v>-13.0069162031321</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0958880900668903</v>
+        <v>16.5755910620363</v>
       </c>
     </row>
   </sheetData>
@@ -731,22 +731,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>10.0679685269244</v>
+        <v>65.1100819848929</v>
       </c>
       <c r="C2" t="n">
-        <v>1.36847492794241</v>
+        <v>28.7969091283215</v>
       </c>
       <c r="D2" t="n">
-        <v>7.35707196482013</v>
+        <v>2.26100939148562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000000000000832017242919729</v>
+        <v>0.0240075214142092</v>
       </c>
       <c r="F2" t="n">
-        <v>7.38580695441114</v>
+        <v>8.66917722730909</v>
       </c>
       <c r="G2" t="n">
-        <v>12.7501300994375</v>
+        <v>121.550986742475</v>
       </c>
     </row>
     <row r="3">
@@ -754,22 +754,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0594505394937821</v>
+        <v>-3.14319113228335</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0167138073353089</v>
+        <v>3.49857204615008</v>
       </c>
       <c r="D3" t="n">
-        <v>3.55697168820353</v>
+        <v>-0.898421153207979</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000412793830919567</v>
+        <v>0.369212231307828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0266920790720343</v>
+        <v>-10.0002663400562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0922089999155275</v>
+        <v>3.71388407548925</v>
       </c>
     </row>
     <row r="4">
@@ -777,22 +777,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.061893801146203</v>
+        <v>2.4771573979275</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0157471866475195</v>
+        <v>1.97203949808905</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.93046723402827</v>
+        <v>1.25613984929202</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000973859405953116</v>
+        <v>0.209406000295846</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0927577198331701</v>
+        <v>-1.3879689944174</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0310298824592342</v>
+        <v>6.34228379027254</v>
       </c>
     </row>
     <row r="5">
@@ -800,22 +800,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00493245143877702</v>
+        <v>0.275874419024579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00344232866767346</v>
+        <v>0.253680313646387</v>
       </c>
       <c r="D5" t="n">
-        <v>1.43288218963434</v>
+        <v>1.08748848130616</v>
       </c>
       <c r="E5" t="n">
-        <v>0.15254931586628</v>
+        <v>0.277125316237694</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00181438877281269</v>
+        <v>-0.221329859309163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0116792916503667</v>
+        <v>0.773078697358331</v>
       </c>
     </row>
     <row r="6">
@@ -823,22 +823,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.105250178523385</v>
+        <v>1.78433742945242</v>
       </c>
       <c r="C6" t="n">
-        <v>0.102623451337283</v>
+        <v>7.54669664813016</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.02559577905316</v>
+        <v>0.236439532771537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.305604156718647</v>
+        <v>0.813147859152927</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.306388447113658</v>
+        <v>-13.0069162031324</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0958880900668888</v>
+        <v>16.5755910620363</v>
       </c>
     </row>
   </sheetData>
@@ -871,13 +871,13 @@
         <v>18</v>
       </c>
       <c r="B2" t="n">
-        <v>12.6179185289343</v>
+        <v>0.811467608788007</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000382066535589583</v>
+        <v>0.367686707174837</v>
       </c>
     </row>
   </sheetData>
